--- a/data/trans_bre/IMC_inf_R2-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IMC_inf_R2-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,35; 17,68</t>
+          <t>-18,06; 18,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-16,13; 25,25</t>
+          <t>-18,17; 24,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-23,56; 17,1</t>
+          <t>-23,22; 16,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-19,11; 22,73</t>
+          <t>-20,91; 24,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-29,84; 46,23</t>
+          <t>-32,65; 44,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-30,47; 78,12</t>
+          <t>-30,06; 67,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-38,67; 47,57</t>
+          <t>-40,04; 44,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-45,0; 104,11</t>
+          <t>-45,76; 115,61</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 6,53</t>
+          <t>-8,14; 6,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-23,15; -7,25</t>
+          <t>-23,22; -7,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-16,31; -1,09</t>
+          <t>-16,58; -1,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-16,45; 2,13</t>
+          <t>-18,35; 1,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-16,37; 15,43</t>
+          <t>-16,83; 16,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-35,8; -12,4</t>
+          <t>-36,07; -12,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-31,23; -2,59</t>
+          <t>-31,24; -2,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-32,59; 4,75</t>
+          <t>-35,68; 3,01</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-18,75; 1,68</t>
+          <t>-18,58; 1,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,93; 12,03</t>
+          <t>-7,23; 13,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-20,2; -2,62</t>
+          <t>-19,91; -2,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-17,11; 3,29</t>
+          <t>-16,24; 2,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-33,3; 3,87</t>
+          <t>-33,73; 2,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-14,62; 26,34</t>
+          <t>-13,38; 30,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-36,99; -5,67</t>
+          <t>-36,73; -3,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-35,84; 7,72</t>
+          <t>-35,52; 7,6</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-31,53; -17,29</t>
+          <t>-30,74; -17,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-18,83; -1,94</t>
+          <t>-19,92; -3,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-18,49; -1,64</t>
+          <t>-18,27; -2,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-25,17; -7,04</t>
+          <t>-25,18; -7,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-69,63; -44,96</t>
+          <t>-68,29; -44,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-45,18; -6,06</t>
+          <t>-46,99; -9,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-51,39; -5,95</t>
+          <t>-51,0; -7,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-66,65; -24,46</t>
+          <t>-66,5; -27,86</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-14,42; -5,16</t>
+          <t>-14,62; -5,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,5; -3,98</t>
+          <t>-13,62; -3,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,65; -5,35</t>
+          <t>-14,63; -4,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-16,87; -5,18</t>
+          <t>-15,83; -4,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-30,69; -11,96</t>
+          <t>-30,91; -13,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-25,27; -8,09</t>
+          <t>-25,56; -6,95</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-31,02; -12,61</t>
+          <t>-31,25; -11,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-41,14; -15,25</t>
+          <t>-38,97; -13,84</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IMC_inf_R2-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IMC_inf_R2-Edad-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad declarado</t>
+          <t>Población con sobrepeso u obesidad declarado por los/as progenitores/as</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-18,06; 18,8</t>
+          <t>-18,69; 20,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-18,17; 24,52</t>
+          <t>-19,83; 22,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-23,22; 16,31</t>
+          <t>-23,71; 15,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-20,91; 24,14</t>
+          <t>-19,24; 24,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-32,65; 44,99</t>
+          <t>-32,37; 50,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-30,06; 67,75</t>
+          <t>-33,2; 66,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-40,04; 44,41</t>
+          <t>-41,05; 42,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-45,76; 115,61</t>
+          <t>-43,32; 116,01</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 6,97</t>
+          <t>-8,91; 6,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-23,22; -7,58</t>
+          <t>-22,85; -6,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-16,58; -1,15</t>
+          <t>-17,01; -1,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-18,35; 1,43</t>
+          <t>-16,77; 1,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-16,83; 16,86</t>
+          <t>-18,08; 15,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-36,07; -12,94</t>
+          <t>-35,14; -10,17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-31,24; -2,46</t>
+          <t>-32,91; -2,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-35,68; 3,01</t>
+          <t>-32,85; 3,82</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-18,58; 1,09</t>
+          <t>-19,68; 1,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 13,11</t>
+          <t>-7,52; 12,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-19,91; -2,08</t>
+          <t>-19,58; -2,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-16,24; 2,99</t>
+          <t>-15,7; 3,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-33,73; 2,27</t>
+          <t>-35,58; 2,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-13,38; 30,21</t>
+          <t>-13,87; 28,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-36,73; -3,81</t>
+          <t>-35,89; -5,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-35,52; 7,6</t>
+          <t>-33,94; 10,38</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-30,74; -17,18</t>
+          <t>-30,98; -17,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-19,92; -3,06</t>
+          <t>-19,19; -2,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-18,27; -2,14</t>
+          <t>-18,42; -2,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-25,18; -7,7</t>
+          <t>-25,27; -6,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-68,29; -44,08</t>
+          <t>-70,1; -45,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-46,99; -9,27</t>
+          <t>-46,07; -6,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-51,0; -7,73</t>
+          <t>-51,78; -6,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-66,5; -27,86</t>
+          <t>-68,28; -23,99</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-14,62; -5,7</t>
+          <t>-14,45; -5,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,62; -3,32</t>
+          <t>-13,6; -3,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,63; -4,48</t>
+          <t>-14,87; -5,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-15,83; -4,76</t>
+          <t>-16,53; -5,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-30,91; -13,46</t>
+          <t>-30,44; -13,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-25,56; -6,95</t>
+          <t>-25,63; -6,89</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-31,25; -11,01</t>
+          <t>-31,9; -12,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-38,97; -13,84</t>
+          <t>-40,01; -13,9</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IMC_inf_R2-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IMC_inf_R2-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,98</t>
+          <t>0,66</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-18,69; 20,49</t>
+          <t>-16,35; 17,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,83; 22,5</t>
+          <t>-16,13; 25,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-23,71; 15,93</t>
+          <t>-23,56; 17,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-19,24; 24,91</t>
+          <t>-21,1; 21,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-32,37; 50,14</t>
+          <t>-29,84; 46,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-33,2; 66,85</t>
+          <t>-30,47; 78,12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-41,05; 42,33</t>
+          <t>-38,67; 47,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-43,32; 116,01</t>
+          <t>-48,41; 95,59</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-7,96</t>
+          <t>-9,82</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-16,94%</t>
+          <t>-20,88%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,91; 6,25</t>
+          <t>-8,03; 6,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-22,85; -6,04</t>
+          <t>-23,15; -7,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-17,01; -1,21</t>
+          <t>-16,31; -1,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-16,77; 1,29</t>
+          <t>-18,6; -0,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-18,08; 15,22</t>
+          <t>-16,37; 15,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-35,14; -10,17</t>
+          <t>-35,8; -12,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-32,91; -2,64</t>
+          <t>-31,23; -2,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-32,85; 3,82</t>
+          <t>-36,54; -0,03</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-6,37</t>
+          <t>-7,35</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-15,19%</t>
+          <t>-17,46%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-19,68; 1,23</t>
+          <t>-18,75; 1,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,52; 12,29</t>
+          <t>-7,93; 12,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-19,58; -2,27</t>
+          <t>-20,2; -2,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-15,7; 3,76</t>
+          <t>-17,38; 2,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-35,58; 2,59</t>
+          <t>-33,3; 3,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-13,87; 28,04</t>
+          <t>-14,62; 26,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-35,89; -5,32</t>
+          <t>-36,99; -5,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-33,94; 10,38</t>
+          <t>-36,03; 5,39</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-15,67</t>
+          <t>-15,11</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-48,17%</t>
+          <t>-45,02%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-30,98; -17,14</t>
+          <t>-31,53; -17,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-19,19; -2,33</t>
+          <t>-18,83; -1,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-18,42; -2,04</t>
+          <t>-18,49; -1,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-25,27; -6,56</t>
+          <t>-23,61; -6,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-70,1; -45,75</t>
+          <t>-69,63; -44,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-46,07; -6,5</t>
+          <t>-45,18; -6,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-51,78; -6,35</t>
+          <t>-51,39; -5,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-68,28; -23,99</t>
+          <t>-61,55; -24,17</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-10,67</t>
+          <t>-10,84</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-27,36%</t>
+          <t>-27,52%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-14,45; -5,91</t>
+          <t>-14,42; -5,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,6; -3,44</t>
+          <t>-13,5; -3,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,87; -5,13</t>
+          <t>-14,65; -5,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-16,53; -5,1</t>
+          <t>-15,8; -5,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-30,44; -13,47</t>
+          <t>-30,69; -11,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-25,63; -6,89</t>
+          <t>-25,27; -8,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-31,9; -12,12</t>
+          <t>-31,02; -12,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-40,01; -13,9</t>
+          <t>-37,33; -15,87</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IMC_inf_R2-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IMC_inf_R2-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -522,7 +531,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad declarado por los/as progenitores/as</t>
+          <t>Población con sobrepeso u obesidad declarado por madres/padres</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-0,11</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3,21</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-4,29</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,66</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-0,21%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,89%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-8,55%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-0.1073440035228468</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>3.207050674059558</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-4.285000818995738</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0.6564807691600005</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.002142466705264732</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.0689195023027611</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.08547884785454875</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.01901088161552687</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-16,35; 17,68</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-16,13; 25,25</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-23,56; 17,1</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-21,1; 21,58</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-29,84; 46,23</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-30,47; 78,12</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-38,67; 47,57</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-48,41; 95,59</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-16.34682799461184</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-16.12969349199329</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-23.55940106929884</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-21.09764196849263</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.2983919997678606</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.3046723642933579</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.3866732440369324</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.4840778021828182</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>17.67894216459419</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>25.24722878404646</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>17.10371893940691</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>21.57947970569094</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.4623099936841503</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.7812415297161244</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.475665434482018</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.9558931795338397</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,71</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-14,86</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-8,53</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-9,82</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-1,58%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-24,44%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-17,41%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-20,88%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-8,03; 6,53</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-23,15; -7,25</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-16,31; -1,09</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-18,6; -0,01</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-16,37; 15,43</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-35,8; -12,4</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-31,23; -2,59</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-36,54; -0,03</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-0.7102612207306513</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-14.8603213777843</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-8.525885560796237</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-9.815456153680913</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.01576167362699289</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.2443803676107593</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.1740535017486829</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.208750946562907</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-8,6</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>3,09</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-11,22</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-7,35</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-17,02%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>6,26%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-22,41%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-17,46%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-8.025169014342069</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-23.14627845025768</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-16.31382748079873</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-18.6037608692554</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.1637104314013179</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.3580494119836029</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.3123022992239959</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.3653964973648923</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-18,75; 1,68</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-7,93; 12,03</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-20,2; -2,62</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-17,38; 2,08</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-33,3; 3,87</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-14,62; 26,34</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-36,99; -5,67</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-36,03; 5,39</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>6.526358223743434</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>-7.250440589660205</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>-1.094038880783775</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>-0.005820653882600587</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.1543327876326565</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>-0.1240430437336383</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>-0.02588888101338673</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>-0.000302706633208213</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +819,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-24,11</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-10,92</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-9,9</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-15,11</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-58,07%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-28,93%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-31,55%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-45,02%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-8.598425765826272</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>3.088295896258558</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-11.22363375253516</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-7.352088489244258</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.1702144444097628</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.06260971732527959</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.2241016962715456</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.1745813629521087</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-31,53; -17,29</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-18,83; -1,94</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-18,49; -1,64</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-23,61; -6,77</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-69,63; -44,96</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-45,18; -6,06</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-51,39; -5,95</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-61,55; -24,17</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-18.74761832433524</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-7.930493938307215</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-20.20221801779508</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-17.37500687300276</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.3330203080585475</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.1462077071536771</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.3698721502999967</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.3603469860861985</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1.683430483017403</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>12.02733943384839</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>-2.620455057204368</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>2.080392130570093</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.03866056049053646</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.2633566395582009</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>-0.05674562043342254</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.05394234652932157</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-24.11048166909238</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-10.9216537399564</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-9.900645751372435</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-15.11455088153859</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.5807086641624717</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.2893105518351068</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.3155349864001213</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.4501731257443515</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-31.53157907068456</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-18.82723108030032</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-18.49393940073319</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-23.60867108489796</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.6963378865409028</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.4517804767557312</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.5138601090741095</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.615508029024464</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>-17.29454858251353</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>-1.935973246182189</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>-1.642343620370425</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>-6.766085151200388</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>-0.4495895326515481</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>-0.06059722990014761</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>-0.05948645913992211</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>-0.2417390238448104</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-10,18</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-8,33</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-9,85</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-10,84</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-22,41%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-16,5%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-22,02%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-27,52%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-14,42; -5,16</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-13,5; -3,98</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-14,65; -5,35</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-15,8; -5,79</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-30,69; -11,96</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-25,27; -8,09</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-31,02; -12,61</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-37,33; -15,87</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-10.17690067285283</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-8.328184433778269</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-9.850454737613596</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-10.83525572403882</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.2240672304047215</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.1649716222927928</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.2202378907336141</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.2751886093047166</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-14.42132587158736</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-13.49891268107203</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-14.65309017052844</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-15.79542258165106</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.3068717838752523</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.2527003554966082</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.3102486501396552</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.3733012769993489</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>-5.159110482671275</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>-3.984103319428525</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>-5.350902873224721</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>-5.788945940171785</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>-0.1195547808536363</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>-0.08087279154362183</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>-0.1261108160223352</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>-0.1587198492215738</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1117,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
